--- a/Result/profitability/6265.xlsx
+++ b/Result/profitability/6265.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.42</v>
       </c>
       <c r="M2" t="n">
-        <v>0.21375</v>
+        <v>0.8462499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>14.29625</v>
+        <v>19.535</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0.63</v>
       </c>
       <c r="M3" t="n">
-        <v>0.32875</v>
+        <v>0.9162499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>15.405</v>
+        <v>18.60125</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>2.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0.57125</v>
+        <v>1.18</v>
       </c>
       <c r="N4" t="n">
-        <v>14.54875</v>
+        <v>19.3525</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.53</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5175</v>
+        <v>1.2375</v>
       </c>
       <c r="N5" t="n">
-        <v>14.93</v>
+        <v>17.8475</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.41</v>
       </c>
       <c r="M6" t="n">
-        <v>0.59</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>13.60625</v>
+        <v>14.33</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.47</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5425</v>
+        <v>1.02375</v>
       </c>
       <c r="N7" t="n">
-        <v>10.1225</v>
+        <v>11.42375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.43625</v>
+        <v>0.8237499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>7.107499999999999</v>
+        <v>7.18125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6265</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1650</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1046</v>
+      </c>
+      <c r="E75" t="n">
+        <v>603</v>
+      </c>
+      <c r="F75" t="n">
+        <v>36.57</v>
+      </c>
+      <c r="G75" t="n">
+        <v>568</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>34.45%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>105</v>
+      </c>
+      <c r="J75" t="n">
+        <v>673</v>
+      </c>
+      <c r="K75" t="n">
+        <v>563</v>
+      </c>
+      <c r="L75" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.8624999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.315</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.8562874251497</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.5900000000000034</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01639799888827143</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-5.818181818181817</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>23.34</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.764172335600907</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
